--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_FUNDACION GLOBALCAJA LA RODA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_FUNDACION GLOBALCAJA LA RODA.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. KELLIER</t>
+          <t>N. CEBRIAN HERNANDEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>58.074</v>
+        <v>53.9676</v>
       </c>
       <c r="E2" t="n">
-        <v>50.8167</v>
+        <v>41.5056</v>
       </c>
       <c r="F2" t="n">
-        <v>7.257200000000001</v>
+        <v>12.4619</v>
       </c>
       <c r="G2" t="n">
-        <v>29.1332</v>
+        <v>43.3582</v>
       </c>
       <c r="H2" t="n">
-        <v>31.2426</v>
+        <v>16.8757</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.1094</v>
+        <v>26.4828</v>
       </c>
       <c r="J2" t="n">
-        <v>50.8197</v>
+        <v>67.32849999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>46.4305</v>
+        <v>29.1729</v>
       </c>
       <c r="L2" t="n">
-        <v>4.389</v>
+        <v>38.1556</v>
       </c>
       <c r="M2" t="n">
-        <v>-21.6863</v>
+        <v>-23.9702</v>
       </c>
       <c r="N2" t="n">
-        <v>-15.1883</v>
+        <v>-12.2971</v>
       </c>
       <c r="O2" t="n">
-        <v>-6.498200000000001</v>
+        <v>-11.6732</v>
       </c>
       <c r="P2" t="n">
-        <v>-19.1147</v>
+        <v>-3.6686</v>
       </c>
       <c r="Q2" t="n">
-        <v>-45.7597</v>
+        <v>-41.3193</v>
       </c>
       <c r="R2" t="n">
-        <v>26.6449</v>
+        <v>37.6501</v>
       </c>
       <c r="S2" t="n">
-        <v>30.9477</v>
+        <v>6.5101</v>
       </c>
       <c r="T2" t="n">
-        <v>21.3393</v>
+        <v>0.4183000000000002</v>
       </c>
       <c r="U2" t="n">
-        <v>9.608699999999999</v>
+        <v>6.0919</v>
       </c>
       <c r="V2" t="n">
-        <v>17.1075</v>
+        <v>7.7677</v>
       </c>
       <c r="W2" t="n">
-        <v>24.4174</v>
+        <v>15.0776</v>
       </c>
       <c r="X2" t="n">
-        <v>-7.3098</v>
+        <v>-7.3099</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. CASTELANOS POLA</t>
+          <t>P. LOPEZ USO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>44.0145</v>
+        <v>49.7803</v>
       </c>
       <c r="E3" t="n">
-        <v>21.0558</v>
+        <v>40.2038</v>
       </c>
       <c r="F3" t="n">
-        <v>22.9594</v>
+        <v>9.5764</v>
       </c>
       <c r="G3" t="n">
-        <v>20.5805</v>
+        <v>40.1844</v>
       </c>
       <c r="H3" t="n">
-        <v>16.231</v>
+        <v>18.4296</v>
       </c>
       <c r="I3" t="n">
-        <v>4.3491</v>
+        <v>21.7548</v>
       </c>
       <c r="J3" t="n">
-        <v>26.0447</v>
+        <v>49.7518</v>
       </c>
       <c r="K3" t="n">
-        <v>19.142</v>
+        <v>21.5525</v>
       </c>
       <c r="L3" t="n">
-        <v>6.902600000000001</v>
+        <v>28.1987</v>
       </c>
       <c r="M3" t="n">
-        <v>-5.464499999999999</v>
+        <v>-9.5669</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.9111</v>
+        <v>-3.1231</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.5535</v>
+        <v>-6.444199999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>2.5099</v>
+        <v>12.936</v>
       </c>
       <c r="Q3" t="n">
-        <v>-23.1695</v>
+        <v>-18.1497</v>
       </c>
       <c r="R3" t="n">
-        <v>25.6795</v>
+        <v>31.0854</v>
       </c>
       <c r="S3" t="n">
-        <v>20.5447</v>
+        <v>2.7383</v>
       </c>
       <c r="T3" t="n">
-        <v>10.1701</v>
+        <v>-1.0495</v>
       </c>
       <c r="U3" t="n">
-        <v>10.3744</v>
+        <v>3.7878</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3793000000000004</v>
+        <v>-6.079000000000001</v>
       </c>
       <c r="W3" t="n">
-        <v>8.0098</v>
+        <v>9.6509</v>
       </c>
       <c r="X3" t="n">
-        <v>-7.6305</v>
+        <v>-15.7299</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N. CEBRIAN HERNANDEZ</t>
+          <t>J. KELLIER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D4" t="n">
-        <v>43.7238</v>
+        <v>43.4831</v>
       </c>
       <c r="E4" t="n">
-        <v>35.2038</v>
+        <v>38.9303</v>
       </c>
       <c r="F4" t="n">
-        <v>8.5204</v>
+        <v>4.552700000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>43.3582</v>
+        <v>29.1332</v>
       </c>
       <c r="H4" t="n">
-        <v>16.8757</v>
+        <v>31.2426</v>
       </c>
       <c r="I4" t="n">
-        <v>26.4828</v>
+        <v>-2.1094</v>
       </c>
       <c r="J4" t="n">
-        <v>67.32849999999999</v>
+        <v>50.8197</v>
       </c>
       <c r="K4" t="n">
-        <v>29.1729</v>
+        <v>46.4305</v>
       </c>
       <c r="L4" t="n">
-        <v>38.1556</v>
+        <v>4.389</v>
       </c>
       <c r="M4" t="n">
-        <v>-23.9702</v>
+        <v>-21.6863</v>
       </c>
       <c r="N4" t="n">
-        <v>-12.2971</v>
+        <v>-15.1883</v>
       </c>
       <c r="O4" t="n">
-        <v>-11.6732</v>
+        <v>-6.498200000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>-3.6686</v>
+        <v>-19.1147</v>
       </c>
       <c r="Q4" t="n">
-        <v>-41.3193</v>
+        <v>-45.7597</v>
       </c>
       <c r="R4" t="n">
-        <v>37.6501</v>
+        <v>26.6449</v>
       </c>
       <c r="S4" t="n">
-        <v>-3.7342</v>
+        <v>16.357</v>
       </c>
       <c r="T4" t="n">
-        <v>-5.8839</v>
+        <v>9.453099999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>2.1498</v>
+        <v>6.904</v>
       </c>
       <c r="V4" t="n">
-        <v>7.7677</v>
+        <v>17.1075</v>
       </c>
       <c r="W4" t="n">
-        <v>15.0776</v>
+        <v>24.4174</v>
       </c>
       <c r="X4" t="n">
-        <v>-7.3099</v>
+        <v>-7.3098</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. LOPEZ USO</t>
+          <t>G. MUKENDI KABANGA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>41.9669</v>
+        <v>36.6269</v>
       </c>
       <c r="E5" t="n">
-        <v>37.4111</v>
+        <v>36.9061</v>
       </c>
       <c r="F5" t="n">
-        <v>4.5555</v>
+        <v>-0.2793999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>40.1844</v>
+        <v>31.2282</v>
       </c>
       <c r="H5" t="n">
-        <v>18.4296</v>
+        <v>28.2677</v>
       </c>
       <c r="I5" t="n">
-        <v>21.7548</v>
+        <v>2.9607</v>
       </c>
       <c r="J5" t="n">
-        <v>49.7518</v>
+        <v>53.0674</v>
       </c>
       <c r="K5" t="n">
-        <v>21.5525</v>
+        <v>42.2841</v>
       </c>
       <c r="L5" t="n">
-        <v>28.1987</v>
+        <v>10.7837</v>
       </c>
       <c r="M5" t="n">
-        <v>-9.5669</v>
+        <v>-21.8391</v>
       </c>
       <c r="N5" t="n">
-        <v>-3.1231</v>
+        <v>-14.0163</v>
       </c>
       <c r="O5" t="n">
-        <v>-6.444199999999999</v>
+        <v>-7.823300000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>12.936</v>
+        <v>-15.6394</v>
       </c>
       <c r="Q5" t="n">
-        <v>-18.1497</v>
+        <v>-44.7945</v>
       </c>
       <c r="R5" t="n">
-        <v>31.0854</v>
+        <v>29.1543</v>
       </c>
       <c r="S5" t="n">
-        <v>-5.075299999999999</v>
+        <v>7.9856</v>
       </c>
       <c r="T5" t="n">
-        <v>-3.842</v>
+        <v>2.02</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.2331</v>
+        <v>5.9658</v>
       </c>
       <c r="V5" t="n">
-        <v>-6.079000000000001</v>
+        <v>13.0518</v>
       </c>
       <c r="W5" t="n">
-        <v>9.6509</v>
+        <v>26.6127</v>
       </c>
       <c r="X5" t="n">
-        <v>-15.7299</v>
+        <v>-13.5609</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. MUKENDI KABANGA</t>
+          <t>J. BOONYASITH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D6" t="n">
-        <v>38.5932</v>
+        <v>36.5471</v>
       </c>
       <c r="E6" t="n">
-        <v>40.3948</v>
+        <v>28.9203</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.801400000000001</v>
+        <v>7.626900000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>31.2282</v>
+        <v>29.454</v>
       </c>
       <c r="H6" t="n">
-        <v>28.2677</v>
+        <v>18.9009</v>
       </c>
       <c r="I6" t="n">
-        <v>2.9607</v>
+        <v>10.5531</v>
       </c>
       <c r="J6" t="n">
-        <v>53.0674</v>
+        <v>41.4231</v>
       </c>
       <c r="K6" t="n">
-        <v>42.2841</v>
+        <v>29.0535</v>
       </c>
       <c r="L6" t="n">
-        <v>10.7837</v>
+        <v>12.3696</v>
       </c>
       <c r="M6" t="n">
-        <v>-21.8391</v>
+        <v>-11.9691</v>
       </c>
       <c r="N6" t="n">
-        <v>-14.0163</v>
+        <v>-10.1524</v>
       </c>
       <c r="O6" t="n">
-        <v>-7.823300000000001</v>
+        <v>-1.8164</v>
       </c>
       <c r="P6" t="n">
-        <v>-15.6394</v>
+        <v>-14.8673</v>
       </c>
       <c r="Q6" t="n">
-        <v>-44.7945</v>
+        <v>-40.3538</v>
       </c>
       <c r="R6" t="n">
-        <v>29.1543</v>
+        <v>25.4861</v>
       </c>
       <c r="S6" t="n">
-        <v>9.952500000000001</v>
+        <v>4.5106</v>
       </c>
       <c r="T6" t="n">
-        <v>5.5085</v>
+        <v>-1.3584</v>
       </c>
       <c r="U6" t="n">
-        <v>4.4438</v>
+        <v>5.8692</v>
       </c>
       <c r="V6" t="n">
-        <v>13.0518</v>
+        <v>17.4494</v>
       </c>
       <c r="W6" t="n">
-        <v>26.6127</v>
+        <v>29.2089</v>
       </c>
       <c r="X6" t="n">
-        <v>-13.5609</v>
+        <v>-11.7596</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. BOONYASITH</t>
+          <t>A. CASTELANOS POLA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D7" t="n">
-        <v>28.3527</v>
+        <v>35.8974</v>
       </c>
       <c r="E7" t="n">
-        <v>22.9903</v>
+        <v>14.7265</v>
       </c>
       <c r="F7" t="n">
-        <v>5.3626</v>
+        <v>21.171</v>
       </c>
       <c r="G7" t="n">
-        <v>29.454</v>
+        <v>20.5805</v>
       </c>
       <c r="H7" t="n">
-        <v>18.9009</v>
+        <v>16.231</v>
       </c>
       <c r="I7" t="n">
-        <v>10.5531</v>
+        <v>4.3491</v>
       </c>
       <c r="J7" t="n">
-        <v>41.4231</v>
+        <v>26.0447</v>
       </c>
       <c r="K7" t="n">
-        <v>29.0535</v>
+        <v>19.142</v>
       </c>
       <c r="L7" t="n">
-        <v>12.3696</v>
+        <v>6.902600000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-11.9691</v>
+        <v>-5.464499999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>-10.1524</v>
+        <v>-2.9111</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.8164</v>
+        <v>-2.5535</v>
       </c>
       <c r="P7" t="n">
-        <v>-14.8673</v>
+        <v>2.5099</v>
       </c>
       <c r="Q7" t="n">
-        <v>-40.3538</v>
+        <v>-23.1695</v>
       </c>
       <c r="R7" t="n">
-        <v>25.4861</v>
+        <v>25.6795</v>
       </c>
       <c r="S7" t="n">
-        <v>-3.6834</v>
+        <v>12.4273</v>
       </c>
       <c r="T7" t="n">
-        <v>-7.2883</v>
+        <v>3.8411</v>
       </c>
       <c r="U7" t="n">
-        <v>3.6048</v>
+        <v>8.5862</v>
       </c>
       <c r="V7" t="n">
-        <v>17.4494</v>
+        <v>0.3793000000000004</v>
       </c>
       <c r="W7" t="n">
-        <v>29.2089</v>
+        <v>8.0098</v>
       </c>
       <c r="X7" t="n">
-        <v>-11.7596</v>
+        <v>-7.6305</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. KASA</t>
+          <t>J. VAQUERO PASCUAL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D8" t="n">
-        <v>25.48</v>
+        <v>28.6256</v>
       </c>
       <c r="E8" t="n">
-        <v>4.0352</v>
+        <v>15.9066</v>
       </c>
       <c r="F8" t="n">
-        <v>21.4447</v>
+        <v>12.7191</v>
       </c>
       <c r="G8" t="n">
-        <v>6.556100000000001</v>
+        <v>19.0238</v>
       </c>
       <c r="H8" t="n">
-        <v>13.3616</v>
+        <v>1.5323</v>
       </c>
       <c r="I8" t="n">
-        <v>-6.8057</v>
+        <v>17.4916</v>
       </c>
       <c r="J8" t="n">
-        <v>12.8029</v>
+        <v>33.764</v>
       </c>
       <c r="K8" t="n">
-        <v>16.2754</v>
+        <v>10.3802</v>
       </c>
       <c r="L8" t="n">
-        <v>-3.472199999999999</v>
+        <v>23.3839</v>
       </c>
       <c r="M8" t="n">
-        <v>-6.2471</v>
+        <v>-14.7406</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.9137</v>
+        <v>-8.847900000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>-3.3334</v>
+        <v>-5.8926</v>
       </c>
       <c r="P8" t="n">
-        <v>8.6882</v>
+        <v>-1.7375</v>
       </c>
       <c r="Q8" t="n">
-        <v>-19.3081</v>
+        <v>-36.299</v>
       </c>
       <c r="R8" t="n">
-        <v>27.9962</v>
+        <v>34.5608</v>
       </c>
       <c r="S8" t="n">
-        <v>12.8</v>
+        <v>4.786799999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>3.7151</v>
+        <v>-0.9459000000000002</v>
       </c>
       <c r="U8" t="n">
-        <v>9.0845</v>
+        <v>5.7328</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.5645</v>
+        <v>6.5529</v>
       </c>
       <c r="W8" t="n">
-        <v>6.8247</v>
+        <v>19.3873</v>
       </c>
       <c r="X8" t="n">
-        <v>-9.3893</v>
+        <v>-12.8344</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. VAQUERO PASCUAL</t>
+          <t>J. KASA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,70 +1108,70 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D9" t="n">
-        <v>20.0229</v>
+        <v>23.259</v>
       </c>
       <c r="E9" t="n">
-        <v>10.1698</v>
+        <v>3.056799999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>9.8535</v>
+        <v>20.2024</v>
       </c>
       <c r="G9" t="n">
-        <v>19.0238</v>
+        <v>6.556100000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>1.5323</v>
+        <v>13.3616</v>
       </c>
       <c r="I9" t="n">
-        <v>17.4916</v>
+        <v>-6.8057</v>
       </c>
       <c r="J9" t="n">
-        <v>33.764</v>
+        <v>12.8029</v>
       </c>
       <c r="K9" t="n">
-        <v>10.3802</v>
+        <v>16.2754</v>
       </c>
       <c r="L9" t="n">
-        <v>23.3839</v>
+        <v>-3.472199999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-14.7406</v>
+        <v>-6.2471</v>
       </c>
       <c r="N9" t="n">
-        <v>-8.847900000000001</v>
+        <v>-2.9137</v>
       </c>
       <c r="O9" t="n">
-        <v>-5.8926</v>
+        <v>-3.3334</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.7375</v>
+        <v>8.6882</v>
       </c>
       <c r="Q9" t="n">
-        <v>-36.299</v>
+        <v>-19.3081</v>
       </c>
       <c r="R9" t="n">
-        <v>34.5608</v>
+        <v>27.9962</v>
       </c>
       <c r="S9" t="n">
-        <v>-3.8156</v>
+        <v>10.5791</v>
       </c>
       <c r="T9" t="n">
-        <v>-6.6826</v>
+        <v>2.7364</v>
       </c>
       <c r="U9" t="n">
-        <v>2.8672</v>
+        <v>7.8425</v>
       </c>
       <c r="V9" t="n">
-        <v>6.5529</v>
+        <v>-2.5645</v>
       </c>
       <c r="W9" t="n">
-        <v>19.3873</v>
+        <v>6.8247</v>
       </c>
       <c r="X9" t="n">
-        <v>-12.8344</v>
+        <v>-9.3893</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>26</v>
       </c>
       <c r="D10" t="n">
-        <v>6.548800000000002</v>
+        <v>14.2317</v>
       </c>
       <c r="E10" t="n">
-        <v>2.837999999999999</v>
+        <v>8.2095</v>
       </c>
       <c r="F10" t="n">
-        <v>3.711</v>
+        <v>6.022099999999999</v>
       </c>
       <c r="G10" t="n">
         <v>5.600099999999999</v>
@@ -1234,13 +1234,13 @@
         <v>23.1695</v>
       </c>
       <c r="S10" t="n">
-        <v>-4.4614</v>
+        <v>3.2212</v>
       </c>
       <c r="T10" t="n">
-        <v>-6.2119</v>
+        <v>-0.8404999999999998</v>
       </c>
       <c r="U10" t="n">
-        <v>1.7503</v>
+        <v>4.0619</v>
       </c>
       <c r="V10" t="n">
         <v>8.693</v>
@@ -1267,13 +1267,13 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>1.1946</v>
+        <v>1.0335</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4889</v>
+        <v>0.1787000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7057</v>
+        <v>0.8549000000000001</v>
       </c>
       <c r="G11" t="n">
         <v>0.9023999999999999</v>
@@ -1312,13 +1312,13 @@
         <v>0.3862</v>
       </c>
       <c r="S11" t="n">
-        <v>0.09929999999999997</v>
+        <v>-0.06209999999999998</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2755</v>
+        <v>-0.0348</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1762</v>
+        <v>-0.02730000000000003</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0323</v>
+        <v>0.08200000000000002</v>
       </c>
       <c r="E12" t="n">
         <v>-0.0697</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1019</v>
+        <v>0.1517</v>
       </c>
       <c r="G12" t="n">
         <v>0.1096</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.07719999999999999</v>
+        <v>-0.02760000000000001</v>
       </c>
       <c r="T12" t="n">
         <v>-0.1104</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0332</v>
+        <v>0.0828</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.2254</v>
+        <v>-0.9497000000000003</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.7842</v>
+        <v>-1.005</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4413000000000002</v>
+        <v>0.05520000000000003</v>
       </c>
       <c r="G13" t="n">
         <v>-1.9119</v>
@@ -1468,13 +1468,13 @@
         <v>1.3516</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9932</v>
+        <v>0.2825</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6349</v>
+        <v>0.1443</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3582</v>
+        <v>0.1384</v>
       </c>
       <c r="V13" t="n">
         <v>-0.2855000000000001</v>
@@ -1501,13 +1501,13 @@
         <v>26</v>
       </c>
       <c r="D14" t="n">
-        <v>-10.4421</v>
+        <v>-3.4852</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2771999999999997</v>
+        <v>3.5316</v>
       </c>
       <c r="F14" t="n">
-        <v>-10.7193</v>
+        <v>-7.0171</v>
       </c>
       <c r="G14" t="n">
         <v>-1.267900000000001</v>
@@ -1546,13 +1546,13 @@
         <v>31.2788</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.2599</v>
+        <v>3.6966</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.6764</v>
+        <v>-0.4215000000000002</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4162</v>
+        <v>4.1183</v>
       </c>
       <c r="V14" t="n">
         <v>-13.8304</v>
@@ -1579,13 +1579,13 @@
         <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>295.3362000000001</v>
+        <v>319.0993</v>
       </c>
       <c r="E15" t="n">
-        <v>223.8277</v>
+        <v>231.0011</v>
       </c>
       <c r="F15" t="n">
-        <v>71.5099</v>
+        <v>88.09780000000001</v>
       </c>
       <c r="G15" t="n">
         <v>222.9507</v>
@@ -1624,13 +1624,13 @@
         <v>294.4433999999999</v>
       </c>
       <c r="S15" t="n">
-        <v>49.24400000000001</v>
+        <v>73.00539999999998</v>
       </c>
       <c r="T15" t="n">
-        <v>6.678100000000001</v>
+        <v>13.8522</v>
       </c>
       <c r="U15" t="n">
-        <v>42.56540000000001</v>
+        <v>59.1543</v>
       </c>
       <c r="V15" t="n">
         <v>48.2422</v>
